--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -43838,7 +43838,7 @@
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
@@ -52398,7 +52398,7 @@
       </c>
       <c r="AX468" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY468" t="inlineStr">
@@ -52503,7 +52503,7 @@
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr">
@@ -53795,7 +53795,7 @@
       </c>
       <c r="AX480" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY480" t="inlineStr">
@@ -53896,7 +53896,7 @@
       </c>
       <c r="AX481" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY481" t="inlineStr">
@@ -70224,7 +70224,7 @@
       </c>
       <c r="AX635" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY635" t="inlineStr">
@@ -82876,7 +82876,7 @@
       </c>
       <c r="AX751" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY751" t="inlineStr">

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -58358,7 +58358,7 @@
       </c>
       <c r="AX523" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
+          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY523" t="inlineStr">

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -43838,7 +43838,7 @@
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
@@ -52398,7 +52398,7 @@
       </c>
       <c r="AX468" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY468" t="inlineStr">
@@ -52503,7 +52503,7 @@
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr">
@@ -53795,7 +53795,7 @@
       </c>
       <c r="AX480" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY480" t="inlineStr">
@@ -53896,7 +53896,7 @@
       </c>
       <c r="AX481" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY481" t="inlineStr">
@@ -58358,7 +58358,7 @@
       </c>
       <c r="AX523" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY523" t="inlineStr">
@@ -70224,7 +70224,7 @@
       </c>
       <c r="AX635" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY635" t="inlineStr">
@@ -82876,7 +82876,7 @@
       </c>
       <c r="AX751" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen, Karina Hälleberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Karina Hälleberg, Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AY751" t="inlineStr">

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -39493,7 +39493,7 @@
         <v>135118935</v>
       </c>
       <c r="B334" t="n">
-        <v>45055</v>
+        <v>45060</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>134979955</v>
       </c>
       <c r="B337" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>134979981</v>
       </c>
       <c r="B339" t="n">
-        <v>92647</v>
+        <v>92689</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>134979983</v>
       </c>
       <c r="B374" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>134979959</v>
       </c>
       <c r="B389" t="n">
-        <v>92547</v>
+        <v>92589</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>134979957</v>
       </c>
       <c r="B393" t="n">
-        <v>92534</v>
+        <v>92576</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>135171917</v>
       </c>
       <c r="B396" t="n">
-        <v>56915</v>
+        <v>56920</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>134979965</v>
       </c>
       <c r="B468" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>134979967</v>
       </c>
       <c r="B469" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>134979960</v>
       </c>
       <c r="B480" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>134979963</v>
       </c>
       <c r="B481" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>134979977</v>
       </c>
       <c r="B516" t="n">
-        <v>92385</v>
+        <v>92427</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>134979968</v>
       </c>
       <c r="B523" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>134979973</v>
       </c>
       <c r="B524" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>134979974</v>
       </c>
       <c r="B525" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>134979976</v>
       </c>
       <c r="B530" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>134979984</v>
       </c>
       <c r="B531" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>134979969</v>
       </c>
       <c r="B534" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62287,7 +62287,7 @@
         <v>134979970</v>
       </c>
       <c r="B536" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -62405,7 +62405,7 @@
         <v>134979972</v>
       </c>
       <c r="B537" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>134979975</v>
       </c>
       <c r="B538" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>134979971</v>
       </c>
       <c r="B555" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -67370,7 +67370,7 @@
         <v>135172253</v>
       </c>
       <c r="B581" t="n">
-        <v>45055</v>
+        <v>45060</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -73307,7 +73307,7 @@
         <v>134979962</v>
       </c>
       <c r="B635" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -86535,7 +86535,7 @@
         <v>134979964</v>
       </c>
       <c r="B751" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -87492,7 +87492,7 @@
         <v>135158670</v>
       </c>
       <c r="B759" t="n">
-        <v>45306</v>
+        <v>45311</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -39855,7 +39855,7 @@
         <v>134979955</v>
       </c>
       <c r="B337" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>134979981</v>
       </c>
       <c r="B339" t="n">
-        <v>92689</v>
+        <v>92716</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>134979959</v>
       </c>
       <c r="B389" t="n">
-        <v>92589</v>
+        <v>92616</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>134979957</v>
       </c>
       <c r="B393" t="n">
-        <v>92576</v>
+        <v>92603</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>134979965</v>
       </c>
       <c r="B468" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>134979967</v>
       </c>
       <c r="B469" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>134979977</v>
       </c>
       <c r="B516" t="n">
-        <v>92427</v>
+        <v>92454</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>134979968</v>
       </c>
       <c r="B523" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>134979973</v>
       </c>
       <c r="B524" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>134979974</v>
       </c>
       <c r="B525" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>134979976</v>
       </c>
       <c r="B530" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62287,7 +62287,7 @@
         <v>134979970</v>
       </c>
       <c r="B536" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -62405,7 +62405,7 @@
         <v>134979972</v>
       </c>
       <c r="B537" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>134979975</v>
       </c>
       <c r="B538" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -73307,7 +73307,7 @@
         <v>134979962</v>
       </c>
       <c r="B635" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -86535,7 +86535,7 @@
         <v>134979964</v>
       </c>
       <c r="B751" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -70861,7 +70861,7 @@
         <v>135755552</v>
       </c>
       <c r="B613" t="n">
-        <v>92727</v>
+        <v>92742</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -70861,7 +70861,7 @@
         <v>135755552</v>
       </c>
       <c r="B613" t="n">
-        <v>92742</v>
+        <v>92743</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -70861,7 +70861,7 @@
         <v>135755552</v>
       </c>
       <c r="B613" t="n">
-        <v>92743</v>
+        <v>92744</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -70861,7 +70861,7 @@
         <v>135755552</v>
       </c>
       <c r="B613" t="n">
-        <v>92744</v>
+        <v>92745</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
